--- a/results/5782_gauss.xlsx
+++ b/results/5782_gauss.xlsx
@@ -413,90 +413,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="n">
-        <v>0</v>
-      </c>
-      <c r="B1" t="n">
-        <v>17.64333161475441</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>0.341</v>
-      </c>
-      <c r="B2" t="n">
-        <v>17.92202222800937</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>0.6819999999999999</v>
-      </c>
-      <c r="B3" t="n">
-        <v>17.17394236873714</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>1.023</v>
-      </c>
-      <c r="B4" t="n">
-        <v>16.07657677402181</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>1.364</v>
-      </c>
-      <c r="B5" t="n">
-        <v>14.50847334761204</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>1.705</v>
-      </c>
-      <c r="B6" t="n">
-        <v>10.4767665665581</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>2.046</v>
-      </c>
-      <c r="B7" t="n">
-        <v>7.969885900920338</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>2.387</v>
-      </c>
-      <c r="B8" t="n">
-        <v>6.399136999810199</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>2.728</v>
-      </c>
-      <c r="B9" t="n">
-        <v>3.649217425779459</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>3.069</v>
-      </c>
-      <c r="B10" t="n">
-        <v>2.039137500096401</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>